--- a/CRVS.xlsx
+++ b/CRVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD690FC-4EFB-4473-B23B-9117629C80E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82037F3A-BCFC-4BF5-A7E3-6905E951CB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24150" yWindow="360" windowWidth="23190" windowHeight="18840" activeTab="1" xr2:uid="{ADAE5EC7-9196-433C-8B4F-1E8F4A6D3099}"/>
+    <workbookView xWindow="9000" yWindow="370" windowWidth="29080" windowHeight="15460" xr2:uid="{ADAE5EC7-9196-433C-8B4F-1E8F4A6D3099}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>Price</t>
   </si>
@@ -63,9 +63,6 @@
     <t>AD</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>Founded: 2014</t>
   </si>
   <si>
@@ -244,6 +241,51 @@
   </si>
   <si>
     <t xml:space="preserve">  Involves multiple Th2 derived cytokines (IL-4, IL-5, IL-13, IL-9, IL-10), but current therapies are limited by their activity on a subset of these cytokines.</t>
+  </si>
+  <si>
+    <t>Cohort 4: 200mg bid for 56 days</t>
+  </si>
+  <si>
+    <t>Cohort 3:</t>
+  </si>
+  <si>
+    <t>n=12 72% EASI vs. n=10 placebo 40%</t>
+  </si>
+  <si>
+    <t>Week 8</t>
+  </si>
+  <si>
+    <t>EASI75</t>
+  </si>
+  <si>
+    <t>Week 16</t>
+  </si>
+  <si>
+    <t>Rinvoq</t>
+  </si>
+  <si>
+    <t>Dupixent</t>
+  </si>
+  <si>
+    <t>Placebo</t>
+  </si>
+  <si>
+    <t>60-73%</t>
+  </si>
+  <si>
+    <t>44-51%</t>
+  </si>
+  <si>
+    <t>12-15%</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Week 8 EASI90</t>
+  </si>
+  <si>
+    <t>Q325</t>
   </si>
 </sst>
 </file>
@@ -385,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -412,8 +454,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -501,13 +548,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>812130</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>75311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>93971</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>36256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -533,6 +580,50 @@
         <a:xfrm>
           <a:off x="1148012" y="4246258"/>
           <a:ext cx="2901341" cy="1565156"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>255204</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>131221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600242</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>88271</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51059338-CF92-83CE-D386-4C0D48FF3F32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1465046" y="8803984"/>
+          <a:ext cx="4435775" cy="2206287"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -862,26 +953,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB602D7-41FF-451F-A8EF-F355DB11C24C}">
   <dimension ref="B2:L13"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -889,22 +980,22 @@
       <c r="J2" t="s">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>5.71</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K2" s="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -913,21 +1004,21 @@
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>62.551281000000003</v>
+        <v>74.681871999999998</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
       </c>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
@@ -938,12 +1029,12 @@
       </c>
       <c r="K4" s="1">
         <f>+K2*K3</f>
-        <v>357.16781451000003</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1120.2280799999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16"/>
@@ -953,19 +1044,19 @@
         <v>3</v>
       </c>
       <c r="K5" s="1">
-        <f>14.841+32.405+15.404</f>
-        <v>62.650000000000006</v>
+        <f>2.867+62.822+11.53</f>
+        <v>77.219000000000008</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
@@ -978,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -994,10 +1085,10 @@
       </c>
       <c r="K7" s="1">
         <f>+K4-K5+K6</f>
-        <v>294.51781450999999</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+        <v>1043.0090799999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
         <v>6</v>
       </c>
@@ -1005,7 +1096,7 @@
         <v>397.255</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J10" t="s">
         <v>7</v>
       </c>
@@ -1013,14 +1104,14 @@
         <v>344.68</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1033,229 +1124,293 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90DE88F6-9437-4973-96E1-BDD6D3D1DC25}">
-  <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O58"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="C3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C5" s="11"/>
       <c r="D5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" s="11"/>
       <c r="D6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C17" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C21" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C41" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="18"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C15" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C17" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C21" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C39" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C40" s="18"/>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C44" t="s">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C45" t="s">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C46" t="s">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C47" t="s">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C48" t="s">
+    <row r="51" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49" s="19">
+      <c r="G51" s="19">
         <f>3.63/5.7-1</f>
         <v>-0.36315789473684212</v>
       </c>
     </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C50" t="s">
+    <row r="52" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C51" t="s">
+    <row r="54" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C52" t="s">
-        <v>65</v>
+    <row r="56" spans="3:15" ht="13" x14ac:dyDescent="0.3">
+      <c r="J56" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N56" t="s">
+        <v>71</v>
+      </c>
+      <c r="O56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="J57" s="20"/>
+      <c r="K57" t="s">
+        <v>74</v>
+      </c>
+      <c r="L57" t="s">
+        <v>75</v>
+      </c>
+      <c r="M57" t="s">
+        <v>76</v>
+      </c>
+      <c r="N57" t="s">
+        <v>80</v>
+      </c>
+      <c r="O57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="J58" t="s">
+        <v>72</v>
+      </c>
+      <c r="K58" t="s">
+        <v>77</v>
+      </c>
+      <c r="L58" t="s">
+        <v>78</v>
+      </c>
+      <c r="M58" t="s">
+        <v>79</v>
+      </c>
+      <c r="N58" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="O58" s="21">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
